--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-01</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -293,7 +293,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -334,16 +334,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -1071,7 +1071,7 @@
     <t>投薬声明の投与量に含まれる日付は、特定の用量の日付を反映しています。たとえば、「2016年11月1日から2016年11月3日まで、毎日1錠を服用し、2016年11月4日から2016年11月7日まで、毎日2錠を服用してください。」この特異性は、患者が標識容器を持ち込む場合、または薬物療法の声明が薬物療法に由来する場合にのみ居住することが予想されます。 / The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>refer dosageInstruction mapping</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -293,7 +293,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -719,10 +719,10 @@
 </t>
   </si>
   <si>
-    <t>薬物測定に関連する遭遇 /エピソード / Encounter / Episode associated with MedicationStatement</t>
-  </si>
-  <si>
-    <t>この薬物測定のコンテキストを確立する遭遇またはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
+    <t>薬物測定に関連するEnounter /エピソード / Encounter / Episode associated with MedicationStatement</t>
+  </si>
+  <si>
+    <t>この薬物測定のコンテキストを確立するEnounterまたはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
   </si>
   <si>
     <t>Event.context</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -563,7 +563,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>アクティブ|完了|エラーに入った|意図した|停止|オンホールド|不明|非テイク / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
+    <t>アクティブ | 完了 | エラー入力 | 意図的 | 停止 | 保留 | 不明 | 未取得 / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
   </si>
   <si>
     <t>服薬状況のを示す。コード表： http://hl7.org/fhir/CodeSystem/medication-statement-status

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -1380,17 +1380,17 @@
   <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.7578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.8203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.8046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1399,26 +1399,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="188.5859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.84375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="140.73046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -715,7 +715,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -913,7 +913,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1017,7 +1017,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1390,7 +1390,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1405,7 +1405,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.84375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -81,13 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このProfileは服薬状況を示すものであり，診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
+    <t>このProfileは服薬状況を示すものであり、診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や，調剤情報，薬剤投与実施情報としては用いられず，それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
+    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や、調剤情報、薬剤投与実施情報としては用いられず、それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -969,7 +969,7 @@
 </t>
   </si>
   <si>
-    <t>投与理由，対象疾患についてのコード</t>
+    <t>投与理由、対象疾患についてのコード</t>
   </si>
   <si>
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
@@ -1062,7 +1062,7 @@
 </t>
   </si>
   <si>
-    <t>この薬剤がどのように服用されたのか，服用すべきだったのかを示す情報</t>
+    <t>この薬剤がどのように服用されたのか、服用すべきだったのかを示す情報</t>
   </si>
   <si>
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -501,7 +501,7 @@
   </si>
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。それ以外に任意のIDを付与してもよい。
-このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
